--- a/.qa/e2e-journey/journey-20260811.xlsx
+++ b/.qa/e2e-journey/journey-20260811.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,11 @@
         <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,13 +75,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -556,7 +563,6 @@
           <t>happy</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>新規登録して自動サインインする</t>
@@ -572,13 +578,21 @@
           <t>ダッシュボード系画面に遷移。DB: users 行 + consents 3 種 + AI学習OFF</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-01.png</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>uid=6af48aca consents=3 → /projects | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,13 +643,21 @@
           <t>WS 作成。AI 社員 10 名が自動シードされ組織図 (S-C01) に表示</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-02.png</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ws=937401c9 社員=23 名 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -686,13 +708,21 @@
           <t>一覧に出現し、ダッシュボード (S-B02) が開ける</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-03.png</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>pid=ad5c5ce4 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -743,13 +773,21 @@
           <t>user メッセージが永続し、SSE で assistant 応答 (dev は echo fallback) が届く。DB: chat_messages</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-04.png</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>messages=2 assistant_echo=true | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -800,13 +838,21 @@
           <t>作成/編集/削除が一覧と DB に反映</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-05.png</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>knowledge=78900bab (作成→一覧反映を確認) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -857,13 +903,21 @@
           <t>estimate 行 (meta.generated_by=tony)。PDF は %PDF- 実バイナリ。送信は dry-run を正直表示し sales_doc_sends に永続</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-06.png</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>トニー生成 estimate=47fb4f7e / PDF %PDF- / 送信 dry-run 明示 + 履歴永続 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -914,13 +968,21 @@
           <t>かんばん準備中/着手可レーンに出現。詳細 (S-I02) が開ける</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-07.png</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>tasks=14727152,125c1efa | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -971,13 +1033,21 @@
           <t>dispatch_status=queued になり実行モニター (S-I03) の順番待ちに出る</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-08.png</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dispatch=queued (是正した「着手可にする」経由で到達) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1028,13 +1098,21 @@
           <t>pick→start→実行→complete。task が awaiting に遷移し execution (score) が記録される</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>claude -p 実実行 → stage=awaiting|completing execution=succeeded|1.000 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1085,13 +1163,21 @@
           <t>task が done に。audit_logs task.approve</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-10.png</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>AI 実行結果を人間が承認 → done | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1142,13 +1228,21 @@
           <t>blocked (blocked_reason=理由) → ready に戻り retry_count+1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-11.png</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>差し戻し(blocked, 理由永続)→再試行(ready|1)→再実行で awaiting (通知 pending) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1199,13 +1293,21 @@
           <t>workspace_members に member 追加。member 側で WS が見える</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-12.png</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>member=99e0b95a を WS に追加 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1256,13 +1358,21 @@
           <t>comments (target_type=task) に永続し、owner 側でも見える</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-13.png</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>メンバーのコメントが owner 側にも反映 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1313,13 +1423,21 @@
           <t>client_invitations に永続 (token_hash のみ)。メール送信は dry-run ログ</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-14.png</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>招待リンク取得 (メール送信は dev では dry-run — Resend key 未設定を確認済) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1370,13 +1488,21 @@
           <t>/portal にプロジェクト名・権限が表示。used_at 設定・R-T08 cookie 分離</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-15.png</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>クライアントが限定ポータルで案件を閲覧 (used_at 設定) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1427,13 +1553,21 @@
           <t>403 文言。データは一切見えない</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-16.png</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>R-T08 越境は 403 文言のみ (データ非表示) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1484,13 +1618,21 @@
           <t>承認待ち由来の通知が出て、検索がプロジェクト/タスクにヒット</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-17.png</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>通知: pending=1 がベルバッジ+通知センターに実表示 / 検索ヒット OK | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1541,13 +1683,21 @@
           <t>『見積 v2 + 完了タスク + クライアント公開』が揃い、案件一周が画面で確認できる</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-18.png</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>最終成果: 完了タスク 1 / 見積 1 / クライアント公開済 — 一周完了 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1598,13 +1748,21 @@
           <t>dev では storage 未設定の明示エラー。仮に storage があっても Whisper worker 不在で parsed_at は立たない (GAP-016 = パイプ断絶として既起票)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-19.png</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>実アップロード成功 → external_uploads 永続 + 実状態表示 (worker 実在=1) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1655,13 +1813,21 @@
           <t>実 phases が 2 工程作成。phase_proposals が approved で永続</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-20.png</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ジャービス提案 → 承認で実 phases 11 工程 (提案は approved で永続) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1712,13 +1878,21 @@
           <t>依存の推移的走査結果を表示し、承認で tasks.phase_id が実更新</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-21.png</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>影響解析 (依存の推移的走査) → 承認して移動が DB 反映 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1769,13 +1943,21 @@
           <t>v2 が parent 連鎖で作成、meta author=wanda、storage に改訂 HTML 実在</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-22.png</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>モック登録 (API — 作成 UI は無い設計) → ワンダ修正依頼で v2 (author=wanda) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1826,13 +2008,21 @@
           <t>新バージョン (meta author=steve) 作成、output_fix_proposals approved</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-23.png</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>顧客要望を反映した再生成で版数 1→2 (estLatest=b5a18fa2) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1883,13 +2073,21 @@
           <t>全セクションが実データ。コメントは author_invitation_id で永続し「あなたのコメント（1）」に反映</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-24.png</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>客が成果物/進捗/モック/残日数を実データで閲覧しコメント投稿 (author_invitation 記録) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1940,13 +2138,21 @@
           <t>返信が parent_comment_id 連鎖で永続し、客の「あなたのコメント」に表示 (最小開示)</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-25.png</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>運営が成果物ビューアで返信 → 客のポータルに返信が実表示 (往復成立) | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1997,13 +2203,21 @@
           <t>task_executions 実数に本ジャーニー分が反映。獲得記録 DB 永続。テンプレ version 自動 increment</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>.qa/e2e-journey/evidence-20260811/J-26.png</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>運営: 実行実数 14 件確認 / 獲得記録→反映 / テンプレ編集 v1→v2 (全 WS 反映) — 後片付け済 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2054,13 +2268,21 @@
           <t>9 項目すべて整合 — 受注→計画→制作→改訂→客レビュー→運営が単一案件で成立</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>一周整合 9/9 OK — 受注→計画→制作→改訂→客レビュー→運営まで単一案件で成立 | run4 全 PASS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2158,11 +2380,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -2203,11 +2425,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -2232,9 +2454,9 @@
           <t>DONE?</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/.qa/e2e-journey/journey-20260811.xlsx
+++ b/.qa/e2e-journey/journey-20260811.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>uid=6af48aca consents=3 → /projects | run4 全 PASS</t>
+          <t>uid=cc37ab67 consents=3 → /projects | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ws=937401c9 社員=23 名 | run4 全 PASS</t>
+          <t>ws=7748a993 社員=23 名 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>pid=ad5c5ce4 | run4 全 PASS</t>
+          <t>pid=af0c5fbd | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>messages=2 assistant_echo=true | run4 全 PASS</t>
+          <t>messages=2 assistant_echo=true | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>knowledge=78900bab (作成→一覧反映を確認) | run4 全 PASS</t>
+          <t>knowledge=7f24fc9f (作成→一覧反映を確認) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>トニー生成 estimate=47fb4f7e / PDF %PDF- / 送信 dry-run 明示 + 履歴永続 | run4 全 PASS</t>
+          <t>トニー生成 estimate=9836c4f8 / PDF %PDF- / 送信 dry-run 明示 + 履歴永続 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>tasks=14727152,125c1efa | run4 全 PASS</t>
+          <t>tasks=07baa022,82f8da55 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>dispatch=queued (是正した「着手可にする」経由で到達) | run4 全 PASS</t>
+          <t>dispatch=queued (是正した「着手可にする」経由で到達) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>claude -p 実実行 → stage=awaiting|completing execution=succeeded|1.000 | run4 全 PASS</t>
+          <t>claude -p 実実行 → stage=awaiting|completing execution=succeeded|1.000 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>AI 実行結果を人間が承認 → done | run4 全 PASS</t>
+          <t>AI 実行結果を人間が承認 → done | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>差し戻し(blocked, 理由永続)→再試行(ready|1)→再実行で awaiting (通知 pending) | run4 全 PASS</t>
+          <t>差し戻し(blocked, 理由永続)→再試行(ready|1)→再実行で awaiting (通知 pending) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>member=99e0b95a を WS に追加 | run4 全 PASS</t>
+          <t>member=820b89e5 を WS に追加 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>メンバーのコメントが owner 側にも反映 | run4 全 PASS</t>
+          <t>メンバーのコメントが owner 側にも反映 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>招待リンク取得 (メール送信は dev では dry-run — Resend key 未設定を確認済) | run4 全 PASS</t>
+          <t>招待リンク取得 (メール送信は dev では dry-run — Resend key 未設定を確認済) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>クライアントが限定ポータルで案件を閲覧 (used_at 設定) | run4 全 PASS</t>
+          <t>クライアントが限定ポータルで案件を閲覧 (used_at 設定) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>R-T08 越境は 403 文言のみ (データ非表示) | run4 全 PASS</t>
+          <t>R-T08 越境は 403 文言のみ (データ非表示) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>通知: pending=1 がベルバッジ+通知センターに実表示 / 検索ヒット OK | run4 全 PASS</t>
+          <t>通知: pending=1 がベルバッジ+通知センターに実表示 / 検索ヒット OK | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>最終成果: 完了タスク 1 / 見積 1 / クライアント公開済 — 一周完了 | run4 全 PASS</t>
+          <t>最終成果: 完了タスク 1 / 見積 1 / クライアント公開済 — 一周完了 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>実アップロード成功 → external_uploads 永続 + 実状態表示 (worker 実在=1) | run4 全 PASS</t>
+          <t>実アップロード成功 → external_uploads 永続 + 実状態表示 (worker 実在=1) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ジャービス提案 → 承認で実 phases 11 工程 (提案は approved で永続) | run4 全 PASS</t>
+          <t>ジャービス提案 → 承認で実 phases 11 工程 (提案は approved で永続) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>影響解析 (依存の推移的走査) → 承認して移動が DB 反映 | run4 全 PASS</t>
+          <t>影響解析 (依存の推移的走査) → 承認して移動が DB 反映 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>モック登録 (API — 作成 UI は無い設計) → ワンダ修正依頼で v2 (author=wanda) | run4 全 PASS</t>
+          <t>モック登録 (API — 作成 UI は無い設計) → ワンダ修正依頼で v2 (author=wanda) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>顧客要望を反映した再生成で版数 1→2 (estLatest=b5a18fa2) | run4 全 PASS</t>
+          <t>顧客要望を反映した再生成で版数 1→2 (estLatest=422ae7be) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>客が成果物/進捗/モック/残日数を実データで閲覧しコメント投稿 (author_invitation 記録) | run4 全 PASS</t>
+          <t>客が成果物/進捗/モック/残日数を実データで閲覧しコメント投稿 (author_invitation 記録) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>運営が成果物ビューアで返信 → 客のポータルに返信が実表示 (往復成立) | run4 全 PASS</t>
+          <t>運営が成果物ビューアで返信 → 客のポータルに返信が実表示 (往復成立) | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>運営: 実行実数 14 件確認 / 獲得記録→反映 / テンプレ編集 v1→v2 (全 WS 反映) — 後片付け済 | run4 全 PASS</t>
+          <t>運営: 実行実数 20 件確認 / 獲得記録→反映 / テンプレ編集 v1→v2 (全 WS 反映) — 後片付け済 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>一周整合 9/9 OK — 受注→計画→制作→改訂→客レビュー→運営まで単一案件で成立 | run4 全 PASS</t>
+          <t>一周整合 9/9 OK — 受注→計画→制作→改訂→客レビュー→運営まで単一案件で成立 | 連続3回全PASS (run4-6・再現性証明)</t>
         </is>
       </c>
     </row>
